--- a/S_数据表/Scene_Template.xlsx
+++ b/S_数据表/Scene_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\YongShi\S_数据表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F325E09-7B46-4154-91B9-D8B975BA62BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A51CC184-BF67-4B39-861A-592DE59F057D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="189">
   <si>
     <t>ID</t>
   </si>
@@ -642,6 +642,10 @@
   </si>
   <si>
     <t>SceneName</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>0;320;100;-20</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -3755,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="K66" s="18" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
